--- a/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
+++ b/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
@@ -8,18 +8,23 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -203,7 +208,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Kuwait Finance House Plc — Cash Flow Summary by Year</a:t>
+              <a:t>Kuwait Finance House Plc — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -401,6 +406,576 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Kuwait Finance House Plc — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>US$'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Kuwait Finance House Plc — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$22:$AD$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>US$'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Kuwait Finance House Plc — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$29:$AL$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>US$'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Kuwait Finance House Plc — Pillar 3 Key Metrics by Year</a:t>
             </a:r>
           </a:p>
@@ -428,7 +1003,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
@@ -446,12 +1021,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,7 +1036,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
@@ -479,12 +1054,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,7 +1069,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
@@ -512,12 +1087,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,7 +1102,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
@@ -545,12 +1120,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,7 +1135,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q10</f>
+              <f>'Overview'!AO10</f>
             </strRef>
           </tx>
           <spPr>
@@ -578,12 +1153,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$10:$V$10</f>
+              <f>'Overview'!$AP$10:$AT$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -660,7 +1235,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -682,10 +1257,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -695,6 +1270,72 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>85</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>129</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -992,7 +1633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:AT39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1015,6 +1656,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1027,14 +1692,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (US$'000)</t>
+          <t>Balance Sheet Summary (US$'000)</t>
         </is>
       </c>
     </row>
@@ -1094,27 +1759,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1123,277 +1788,277 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>-75732</v>
+        <v>2576896</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-131665</v>
+        <v>2737527</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>72516</v>
+        <v>2923898</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>34665</v>
+        <v>2835743</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>264870</v>
+        <v>2996510</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>264870</v>
+        <v>2996510</v>
       </c>
       <c r="K6" t="n">
-        <v>34665</v>
+        <v>2835743</v>
       </c>
       <c r="L6" t="n">
-        <v>72516</v>
+        <v>2923898</v>
       </c>
       <c r="M6" t="n">
-        <v>-131665</v>
+        <v>2737527</v>
       </c>
       <c r="N6" t="n">
-        <v>-75732</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>2576896</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>22.4</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>19.9</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>19.4</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>19.2</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>20.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
+          <t>Financing receivables / Loans and advances</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-14974</v>
+        <v>1524604</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>257136</v>
+        <v>1512591</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-67619</v>
+        <v>1536066</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-227909</v>
+        <v>1454873</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-34076</v>
+        <v>1602103</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
+          <t>Financing receivables / Loans and advances</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-34076</v>
+        <v>1602103</v>
       </c>
       <c r="K7" t="n">
-        <v>-227909</v>
+        <v>1454873</v>
       </c>
       <c r="L7" t="n">
-        <v>-67619</v>
+        <v>1536066</v>
       </c>
       <c r="M7" t="n">
-        <v>257136</v>
+        <v>1512591</v>
       </c>
       <c r="N7" t="n">
-        <v>-14974</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>1524604</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>22.5</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>19.9</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>19.4</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>19.2</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>20.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net cash used in financing activities</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-31875</v>
+        <v>2149033</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-32014</v>
+        <v>2259618</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-31260</v>
+        <v>2509823</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-11777</v>
+        <v>2359144</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-11954</v>
+        <v>2515820</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net cash used in financing activities</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-11954</v>
+        <v>2515820</v>
       </c>
       <c r="K8" t="n">
-        <v>-11777</v>
+        <v>2359144</v>
       </c>
       <c r="L8" t="n">
-        <v>-31260</v>
+        <v>2509823</v>
       </c>
       <c r="M8" t="n">
-        <v>-32014</v>
+        <v>2259618</v>
       </c>
       <c r="N8" t="n">
-        <v>-31875</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>2149033</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AP8" t="n">
         <v>10.5</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>12.3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
         <v>11.9</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AS8" t="n">
         <v>13.7</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AT8" t="n">
         <v>14.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at 31 December</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>593223</v>
+        <v>332609</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>752166</v>
+        <v>347279</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>664122</v>
+        <v>333754</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>692136</v>
+        <v>330285</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>891390</v>
+        <v>322749</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at 31 December</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>891390</v>
+        <v>322749</v>
       </c>
       <c r="K9" t="n">
-        <v>692136</v>
+        <v>330285</v>
       </c>
       <c r="L9" t="n">
-        <v>664122</v>
+        <v>333754</v>
       </c>
       <c r="M9" t="n">
-        <v>752166</v>
+        <v>347279</v>
       </c>
       <c r="N9" t="n">
-        <v>593223</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>332609</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="AP9" t="n">
         <v>486.4</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>392.5</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AR9" t="n">
         <v>662.5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AS9" t="n">
         <v>385.4</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AT9" t="n">
         <v>592.3</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="AP10" t="n">
         <v>136.2</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AQ10" t="n">
         <v>127.4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AR10" t="n">
         <v>133</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AS10" t="n">
         <v>119.4</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AT10" t="n">
         <v>139</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
+          <t>Profit &amp; Loss Summary (US$'000)</t>
         </is>
       </c>
     </row>
@@ -1428,177 +2093,831 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>82052</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>95956</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>102673</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>79242</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>52715</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>52715</v>
+      </c>
+      <c r="S13" t="n">
+        <v>79242</v>
+      </c>
+      <c r="T13" t="n">
+        <v>102673</v>
+      </c>
+      <c r="U13" t="n">
+        <v>95956</v>
+      </c>
+      <c r="V13" t="n">
+        <v>82052</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expense</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>43777</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>42645</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>36790</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>28286</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>30763</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Total operating expense</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>30763</v>
+      </c>
+      <c r="S14" t="n">
+        <v>28286</v>
+      </c>
+      <c r="T14" t="n">
+        <v>36790</v>
+      </c>
+      <c r="U14" t="n">
+        <v>42645</v>
+      </c>
+      <c r="V14" t="n">
+        <v>43777</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Net profit after tax</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>22420</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>39218</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>46986</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>39462</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>18893</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Net profit after tax</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>18893</v>
+      </c>
+      <c r="S15" t="n">
+        <v>39462</v>
+      </c>
+      <c r="T15" t="n">
+        <v>46986</v>
+      </c>
+      <c r="U15" t="n">
+        <v>39218</v>
+      </c>
+      <c r="V15" t="n">
+        <v>22420</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (US$'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>347279</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>333754</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>330285</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>322749</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>276871</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>276871</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>322749</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>330285</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>333754</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>347279</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (Bank/solo basis, ties to the equity sheet)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>15330</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>43525</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>23469</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>17536</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>55841</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (Bank/solo basis, ties to the equity sheet)</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>55841</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>17536</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>23469</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>43525</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>15330</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other equity movements, net</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-30000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>332609</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>347279</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>333754</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>330285</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>322749</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>322749</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>330285</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>333754</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>347279</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>332609</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (US$'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-75732</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-131665</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>72516</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>34665</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>264870</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>264870</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>34665</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>72516</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>-131665</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-75732</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-14974</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>257136</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-67619</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-227909</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-34076</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>-34076</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-227909</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-67619</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>257136</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-14974</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net cash used in financing activities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-31875</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-32014</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-31260</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-11777</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-11954</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Net cash used in financing activities</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>-11954</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-11777</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-31260</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>-32014</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-31875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at 31 December</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>593223</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>752166</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>664122</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>692136</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>891390</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at 31 December</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>891390</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>692136</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>664122</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>752166</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>593223</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>20.1%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>19.2%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>19.4%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>19.9%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>22.4%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>20.1%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>19.2%</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>19.4%</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>19.9%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>22.5%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>14.2%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>13.7%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>11.9%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>12.3%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>10.5%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>592.3%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>385.4%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>662.5%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>392.5%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>486.4%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>139.0%</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>119.4%</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>133.0%</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>127.4%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>136.2%</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Note: Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) converted to a Shariah-compliant (Islamic) bank during FY2024 under new ownership - see the Cash Flow Statement sheet's ENTITY NOTE. Figures are US$, not converted to GBP (native-currency presentation, consistent with sibling USD-reporting banks in this batch). Total RWAs are calculated (Own Funds / Total Capital ratio), not directly disclosed. Figures are duplicated from the detail sheets for at-a-glance trend viewing.</t>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Note: Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) converted to a Shariah-compliant (Islamic) bank during FY2024 under new ownership - see the Balance Sheet sheet's ENTITY NOTE. Figures are US$, not converted to GBP (native-currency presentation, consistent with sibling USD-reporting banks in this batch). Balance Sheet and Statement of Changes in Equity are Bank/solo basis; Profit &amp; Loss is necessarily Consolidated (Group) basis - this entity does not publish a standalone Bank income statement (see the Balance Sheet sheet's BASIS NOTE) - so the equity-changes block above uses the equity sheet's own Bank-basis comprehensive income, not the Group P&amp;L's OCI total. Total RWAs is independently derived two ways (Own Funds/Total Capital ratio on the Total RWAs sheet; summed Pillar 1 capital requirement components x12.5 on the RWA Breakdown sheet) since no single RWA figure is directly disclosed - both agree within 0.2%. Figures are duplicated from the detail sheets for at-a-glance trend viewing.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1611,7 +2930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1625,7 +2944,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Leverage Ratio</t>
+          <t>Kuwait Finance House Plc — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
@@ -1671,37 +2990,44 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Leverage ratio</t>
+          <t>Tier 1 ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>10.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="280" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+          <t>22.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: No Additional Tier 1 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout. A small Tier 2 balance ($799k) exists only in FY2021 (see Total Capital), fully amortised/repaid by FY2022 onward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
@@ -1712,8 +3038,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1739,14 +3066,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — LCR</t>
+          <t>Kuwait Finance House Plc — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>USD m</t>
         </is>
       </c>
     </row>
@@ -1785,33 +3112,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Liquidity Coverage Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>592.3%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>385.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>662.5%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>392.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>486.4%</t>
-        </is>
+          <t>Total capital / Own Funds</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>319.8</v>
       </c>
     </row>
     <row r="6" ht="280" customHeight="1">
@@ -1853,7 +3170,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — NSFR</t>
+          <t>Kuwait Finance House Plc — Total Capital Ratio</t>
         </is>
       </c>
     </row>
@@ -1899,32 +3216,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio</t>
+          <t>Total capital ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>139.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>133.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>136.2%</t>
+          <t>22.5%</t>
         </is>
       </c>
     </row>
@@ -1948,6 +3265,653 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted exposure amount (calculated)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1618.4</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1649.3</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1666</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1530.2</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1421.3</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Total RWAs are NOT directly disclosed in the source - calculated as Own Funds / Total Capital ratio for each year (see sheet-level source note). Treat as an approximation consistent with the source's own rounded percentages, not a directly-quoted figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
+FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Derived (x12.5) from the Pillar 3 appendix's own 'minimum capital requirements under Pillar 1' table by risk category - RWAs are not directly disclosed as a category-level figure, but the underlying capital requirement components are. USD'000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (USD'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (USD'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (USD'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (USD'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (USD'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Credit and counterparty risk RWA (Standardised Approach)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1407550</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1394450</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1490975</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1304388</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1206525</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Market risk RWA (Position Risk Requirement)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>38638</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>63925</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>23488</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>62513</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>74988</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Credit value adjustment (CVA) RWA</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>26900</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>31313</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>39650</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk RWA (Basic Indicator Approach)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>165975</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>162913</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>118550</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>120875</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>138150</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total RWAs (derived from disclosed Pillar 1 capital requirement components)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1617663</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1648188</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1664325</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1527425</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1423413</v>
+      </c>
+    </row>
+    <row r="10" ht="380" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
+FY2025/FY2024: p.83-84 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.
+RWA BREAKDOWN METHOD: the source discloses 'The minimum capital requirements under Pillar 1' by risk category every year (Credit and counterparty risk capital requirement (SA); Market risk capital requirement; Credit value adjustment capital requirement; Operational risk capital requirement (BIA)) but never a category-level RWA figure directly. Each category's RWA-equivalent is calculated here as capital requirement / 8% (i.e. x12.5), the standard Basel III relationship between capital requirement and RWA under the Standardised Approach. The resulting Total RWAs (this sheet's own component sum) differs from the Total RWAs sheet's Own-Funds/Total-Capital-ratio-based calculation by under 0.2% every year - both are legitimate derivations from disclosed figures, neither is a directly-quoted 'Total RWAs' line item, and the small gap is an immaterial reconciliation-methodology difference, not a data error.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:F10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — Leverage Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>13.7%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>11.9%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>12.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>10.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="280" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
+FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>592.3%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>385.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>662.5%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>392.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>486.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="280" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
+FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>139.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>119.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>133.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>127.4%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>136.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="280" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
+FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2071,6 +4035,2049 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="95" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — Bank Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bank/solo basis, US$'000. Formerly Ahli United Bank (UK) PLC. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (US$'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (US$'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (US$'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (US$'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (US$'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances with central banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>350734</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>477039</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>302738</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>451104</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>675547</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Deposits with banks</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>242489</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>275127</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>365605</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>245974</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>221740</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Financing receivables / Loans and advances</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1524604</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1512591</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1536066</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1454873</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1602103</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Financial investments</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>419996</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>397718</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>658778</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>582585</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>412144</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>6952</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>41151</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>34717</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>56979</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>18040</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Investment in joint venture</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Investments in group undertakings</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Premises and equipment</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>2436</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>4058</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5311</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>10618</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>5599</v>
+      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Investment property</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n">
+        <v>278</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>354</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Returns receivable and similar assets / Interest receivable and other assets</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>19310</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>24659</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>15409</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>12994</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>8682</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Current tax asset</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1233</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>1769</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>1515</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>274</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax asset</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Retirement benefit scheme</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>3509</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>3105</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3347</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>24381</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>46616</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2576896</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2737527</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2923898</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2835743</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>2996510</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Deposits from banks</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>23106</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>59630</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>11164</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>86543</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>84073</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Customer deposits</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>2149033</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>2259618</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>2509823</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>2359144</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>2515820</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Borrowings under repurchase agreements</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>12582</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>4694</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>13253</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>16006</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>21690</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Returns payable and similar liabilities / Interest payable and other liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>57607</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>62898</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>53969</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>27532</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax liability</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>1959</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>3408</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>1935</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>8303</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>14663</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Subordinated liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>9462</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>9983</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2244287</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>2390248</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>2590144</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>2505458</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>2673761</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ordinary share capital</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>200080</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>200080</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>200080</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>200080</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>200080</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>132529</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>147199</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>133674</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>130205</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>122669</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>332609</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>347279</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>333754</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>330285</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>322749</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2576896</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>2737527</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>2923898</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>2835743</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>2996510</v>
+      </c>
+    </row>
+    <row r="35" ht="420" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Kuwait Finance House Plc's (formerly Ahli United Bank (UK) PLC's) own Annual Report and Financial Statements, from Companies House filings:
+FY2025: Bank Balance Sheet p.27, Consolidated Statement of Income p.24, Consolidated Statement of Comprehensive Income p.25, Bank Statement of Changes in Equity p.30-31 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2024: Bank Balance Sheet p.28, Consolidated Statement of Income p.25, Consolidated Statement of Comprehensive Income p.26, Bank Statement of Changes in Equity p.31 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Bank Balance Sheet p.24, Consolidated Statement of Income p.21, Consolidated Statement of Comprehensive Income p.22, Bank Statement of Changes in Equity p.28 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQxNzM5MjkxNGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Bank Balance Sheet p.23, Consolidated Statement of Income p.20, Consolidated Statement of Comprehensive Income p.21, Bank Statement of Changes in Equity p.27 (own report) - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Bank Balance Sheet p.17, Consolidated Statement of Income (unpaginated, follows p.13), Consolidated Statement of Comprehensive Income p.15, Bank Statement of Changes in Equity p.21 (own report) - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM0MTg2NjEyNWFkaXF6a2N4/document?format=pdf&amp;download=0
+ENTITY NOTE: Kuwait Finance House Plc (FRN 131818, Companies House 00877859) was formerly Ahli United Bank (UK) PLC - renamed following its 2024 conversion to a Shariah-compliant (Islamic) bank under new ownership (Kuwait Finance House Group), confirmed by the FY2024/FY2025 Annual Reports' own Shariah Supervisory Board report describing 'the recent conversion of the Bank'. This is a genuine, disclosed business-model change, not a data anomaly: FY2021-FY2023 use conventional banking terminology (Loans and advances, Interest income/expense/receivable/payable); FY2024-FY2025 use Islamic-finance terminology (Financing receivables, Returns receivable/payable) for the functionally equivalent line items, kept as each year's own originally-printed labels rather than forced into a single common wording. Reports in USD'000 (Bank/solo basis) - all Companies House filings are fully scanned/image-only, transcribed via targeted page-image reads, not full-document OCR. Kept in native USD (not converted to GBP), consistent with sibling USD-reporting banks built in this same batch (e.g. Itau BBA International plc).
+BASIS NOTE: this entity takes the exemption in s.408 Companies Act 2006 and does not present a standalone Bank/solo income statement in any year - only a Consolidated (Group) income statement and comprehensive income statement are published, each year's own Bank Balance Sheet page noting the Bank's own profit-after-tax figure separately (used here to build the Statement of Changes in Equity, which the Bank DOES publish on a solo basis every year). The Balance Sheet and Statement of Changes in Equity sheets in this workbook are therefore Bank/solo basis (consistent with the existing Cash Flow Statement sheet), while the Profit &amp; Loss sheet is necessarily Consolidated (Group) basis - the only income statement this entity discloses. Group and Bank scope differ only immaterially here (a small non-trading subsidiary), so the two bases are not directly comparable line-by-line but both are genuine, source-disclosed figures, not derived or estimated.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A35:F35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="95" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — Profit &amp; Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated (Group) basis - see BASIS NOTE at bottom (this entity does not publish a standalone Bank income statement). US$'000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (US$'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (US$'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (US$'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (US$'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (US$'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Financing and similar income / Interest income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>143932</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>185131</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>178840</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>86307</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>50477</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Financing and similar cost / Interest expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-78199</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-110078</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-94224</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-30047</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-13505</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net financing and similar income / Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>65733</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>75053</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>84616</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>56260</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>36972</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Net fees and commissions</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>7846</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>6498</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>8147</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>11141</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Investment income</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>2571</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>9444</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>4545</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>6241</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Other operating income</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>5902</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>4961</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5365</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>5600</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>3149</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Fees and other income</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>16319</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>20903</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>18057</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>22982</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>15743</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>82052</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>95956</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>102673</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>79242</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>52715</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Credit provision loss/(recovery)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>-8012</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-1415</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-4718</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-397</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Net operating income</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>74040</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>94541</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>97955</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>78845</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>54597</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>-25784</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>-24276</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-20490</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-15720</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-17147</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>-2207</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>-1990</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>-2036</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-3106</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-3366</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-15786</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-16379</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-14264</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-9460</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-10250</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses (total)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>43777</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>42645</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>36790</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>28286</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>30763</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>30263</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>51896</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>61165</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>50559</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>23834</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Tax expense</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-7843</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-12678</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-14179</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-11097</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-4941</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Net profit after tax</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>22420</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>39218</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>46986</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>39462</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>18893</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Net change in pension fund reserve</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-17</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>-242</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-20082</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-17605</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>28081</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Net change in fair value of investments</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>-5243</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>4762</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>-3824</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>-4250</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>8495</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Exchange differences on translating sterling share capital</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Net change in fair value of cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-92</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-64</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-5255</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>4521</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-23995</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-21926</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>36948</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>17165</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>43739</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>22991</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>17536</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>55841</v>
+      </c>
+    </row>
+    <row r="30" ht="420" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Kuwait Finance House Plc's (formerly Ahli United Bank (UK) PLC's) own Annual Report and Financial Statements, from Companies House filings:
+FY2025: Bank Balance Sheet p.27, Consolidated Statement of Income p.24, Consolidated Statement of Comprehensive Income p.25, Bank Statement of Changes in Equity p.30-31 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2024: Bank Balance Sheet p.28, Consolidated Statement of Income p.25, Consolidated Statement of Comprehensive Income p.26, Bank Statement of Changes in Equity p.31 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Bank Balance Sheet p.24, Consolidated Statement of Income p.21, Consolidated Statement of Comprehensive Income p.22, Bank Statement of Changes in Equity p.28 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQxNzM5MjkxNGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Bank Balance Sheet p.23, Consolidated Statement of Income p.20, Consolidated Statement of Comprehensive Income p.21, Bank Statement of Changes in Equity p.27 (own report) - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Bank Balance Sheet p.17, Consolidated Statement of Income (unpaginated, follows p.13), Consolidated Statement of Comprehensive Income p.15, Bank Statement of Changes in Equity p.21 (own report) - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM0MTg2NjEyNWFkaXF6a2N4/document?format=pdf&amp;download=0
+ENTITY NOTE: Kuwait Finance House Plc (FRN 131818, Companies House 00877859) was formerly Ahli United Bank (UK) PLC - renamed following its 2024 conversion to a Shariah-compliant (Islamic) bank under new ownership (Kuwait Finance House Group), confirmed by the FY2024/FY2025 Annual Reports' own Shariah Supervisory Board report describing 'the recent conversion of the Bank'. This is a genuine, disclosed business-model change, not a data anomaly: FY2021-FY2023 use conventional banking terminology (Loans and advances, Interest income/expense/receivable/payable); FY2024-FY2025 use Islamic-finance terminology (Financing receivables, Returns receivable/payable) for the functionally equivalent line items, kept as each year's own originally-printed labels rather than forced into a single common wording. Reports in USD'000 (Bank/solo basis) - all Companies House filings are fully scanned/image-only, transcribed via targeted page-image reads, not full-document OCR. Kept in native USD (not converted to GBP), consistent with sibling USD-reporting banks built in this same batch (e.g. Itau BBA International plc).
+BASIS NOTE: this entity takes the exemption in s.408 Companies Act 2006 and does not present a standalone Bank/solo income statement in any year - only a Consolidated (Group) income statement and comprehensive income statement are published, each year's own Bank Balance Sheet page noting the Bank's own profit-after-tax figure separately (used here to build the Statement of Changes in Equity, which the Bank DOES publish on a solo basis every year). The Balance Sheet and Statement of Changes in Equity sheets in this workbook are therefore Bank/solo basis (consistent with the existing Cash Flow Statement sheet), while the Profit &amp; Loss sheet is necessarily Consolidated (Group) basis - the only income statement this entity discloses. Group and Bank scope differ only immaterially here (a small non-trading subsidiary), so the two bases are not directly comparable line-by-line but both are genuine, source-disclosed figures, not derived or estimated.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A30:F30"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bank/solo basis, chronological roll-forward oldest to newest. Equity reconciliation ladder confirmed: every year's own closing balance ties exactly to both the next year's own opening balance and that year's own Balance Sheet Total equity - zero plug rows needed anywhere across all 5 years. US$'000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Ordinary share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Share premium</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Cash flow hedge reserve</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Other reserves / Fair value reserve</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>200080</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n">
+        <v>951</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>75712</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>276871</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Net profit after tax for the year</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n">
+        <v>18893</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>18893</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Net change in fair value of cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n">
+        <v>373</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Net change in fair value of investments</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n">
+        <v>8495</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n">
+        <v>8495</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Net change in pension fund reserve</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n">
+        <v>28081</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>28081</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Exchange differences on translating sterling share capital</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Dividend paid to parent undertaking</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2021 (FY2021 closing / FY2022 opening)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>200080</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n">
+        <v>9819</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>112722</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>322749</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Net profit after tax for the year</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n">
+        <v>39462</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>39462</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Net change in fair value of cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n">
+        <v>-64</v>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n">
+        <v>-64</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Net change in fair value of investments</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n">
+        <v>-4250</v>
+      </c>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n">
+        <v>-4250</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Net change in pension fund reserve</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n">
+        <v>-17605</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-17605</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Reclassification of net changes in fair value through OCI investments upon derecognition</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>318</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-318</v>
+      </c>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Exchange differences on translating sterling share capital</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n">
+        <v>-7</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Dividend paid to parent undertaking</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2022 (FY2022 closing / FY2023 opening - Other reserves 5,823 here becomes Cash flow hedge reserve 92 + Fair value reserve 5,731 in the source's own FY2023 presentation, split below)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>200080</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>5731</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>124254</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>330285</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Net profit after tax for the year</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n">
+        <v>47464</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>47464</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Net change in fair value of cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n">
+        <v>-92</v>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n">
+        <v>-92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Net change in fair value of investments</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n">
+        <v>-3824</v>
+      </c>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n">
+        <v>-3824</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Net change in pension fund reserve</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n">
+        <v>-20082</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-20082</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Exchange differences on translating sterling share capital</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Dividend paid to parent undertaking</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-20000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2023 (FY2023 closing / FY2024 opening)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>200080</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1907</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>131639</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>333754</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Net profit after tax for the year</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n">
+        <v>39450</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>39450</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Net change in fair value of investments</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n">
+        <v>4316</v>
+      </c>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n">
+        <v>4316</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Net change in pension fund reserve</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n">
+        <v>-242</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-242</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Reclassification of net changes in fair value through OCI investments</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n">
+        <v>446</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-446</v>
+      </c>
+      <c r="G30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Exchange differences on translating sterling share capital</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Dividend paid to parent undertaking</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-30000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2024 (FY2024 closing / FY2025 opening)</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>200080</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>6669</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>140402</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>347279</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Net profit after tax for the year</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n">
+        <v>20585</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>20585</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Net change in fair value of investments</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n">
+        <v>-5243</v>
+      </c>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n">
+        <v>-5243</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Net change in pension fund reserve</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n">
+        <v>-17</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Exchange differences on translating sterling share capital</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Dividend paid to parent undertaking</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>-30000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Balance at 31 December 2025 (FY2025 closing)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>200080</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>1426</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>130975</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>332609</v>
+      </c>
+    </row>
+    <row r="41" ht="150" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Sources - all figures are Kuwait Finance House Plc's (formerly Ahli United Bank (UK) PLC's) own Annual Report and Financial Statements, from Companies House filings:
+FY2025: Bank Balance Sheet p.27, Consolidated Statement of Income p.24, Consolidated Statement of Comprehensive Income p.25, Bank Statement of Changes in Equity p.30-31 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2024: Bank Balance Sheet p.28, Consolidated Statement of Income p.25, Consolidated Statement of Comprehensive Income p.26, Bank Statement of Changes in Equity p.31 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Bank Balance Sheet p.24, Consolidated Statement of Income p.21, Consolidated Statement of Comprehensive Income p.22, Bank Statement of Changes in Equity p.28 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQxNzM5MjkxNGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022: Bank Balance Sheet p.23, Consolidated Statement of Income p.20, Consolidated Statement of Comprehensive Income p.21, Bank Statement of Changes in Equity p.27 (own report) - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021: Bank Balance Sheet p.17, Consolidated Statement of Income (unpaginated, follows p.13), Consolidated Statement of Comprehensive Income p.15, Bank Statement of Changes in Equity p.21 (own report) - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM0MTg2NjEyNWFkaXF6a2N4/document?format=pdf&amp;download=0
+ENTITY NOTE: Kuwait Finance House Plc (FRN 131818, Companies House 00877859) was formerly Ahli United Bank (UK) PLC - renamed following its 2024 conversion to a Shariah-compliant (Islamic) bank under new ownership (Kuwait Finance House Group), confirmed by the FY2024/FY2025 Annual Reports' own Shariah Supervisory Board report describing 'the recent conversion of the Bank'. This is a genuine, disclosed business-model change, not a data anomaly: FY2021-FY2023 use conventional banking terminology (Loans and advances, Interest income/expense/receivable/payable); FY2024-FY2025 use Islamic-finance terminology (Financing receivables, Returns receivable/payable) for the functionally equivalent line items, kept as each year's own originally-printed labels rather than forced into a single common wording. Reports in USD'000 (Bank/solo basis) - all Companies House filings are fully scanned/image-only, transcribed via targeted page-image reads, not full-document OCR. Kept in native USD (not converted to GBP), consistent with sibling USD-reporting banks built in this same batch (e.g. Itau BBA International plc).
+BASIS NOTE: this entity takes the exemption in s.408 Companies Act 2006 and does not present a standalone Bank/solo income statement in any year - only a Consolidated (Group) income statement and comprehensive income statement are published, each year's own Bank Balance Sheet page noting the Bank's own profit-after-tax figure separately (used here to build the Statement of Changes in Equity, which the Bank DOES publish on a solo basis every year). The Balance Sheet and Statement of Changes in Equity sheets in this workbook are therefore Bank/solo basis (consistent with the existing Cash Flow Statement sheet), while the Profit &amp; Loss sheet is necessarily Consolidated (Group) basis - the only income statement this entity discloses. Group and Bank scope differ only immaterially here (a small non-trading subsidiary), so the two bases are not directly comparable line-by-line but both are genuine, source-disclosed figures, not derived or estimated.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A41:G41"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3071,16 +7078,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="76" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3091,433 +7098,373 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — CET1 Capital</t>
+          <t>Kuwait Finance House Plc — Asset Quality</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>Financing receivables / Loans and advances to customers, IFRS 9 stage 1/2/3 gross carrying amount and impairment allowance roll-forward (Note 13). US$'000.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (US$'000)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (US$'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (US$'000)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (US$'000)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (US$'000)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>325.3</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>316.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>323.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="6" ht="280" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
-FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Financing receivables / Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Gross carrying amount</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1543237</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1522372</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1543909</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1457822</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1605505</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Impairment allowance</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-18633</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-9781</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-7843</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-2949</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-3402</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net carrying amount</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1524604</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1512591</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1536066</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1454873</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1602103</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Gross carrying amount, by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 (12-month ECL)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1276906</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1359230</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1409031</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1316924</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1446060</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 (lifetime ECL, not credit-impaired)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>144165</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>75245</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>79810</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>94435</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>131646</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 (lifetime ECL, credit-impaired)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>122166</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>87897</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>55068</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>46463</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>27799</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Impairment allowance, by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1 (12-month ECL)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>283</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>208</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2 (lifetime ECL, not credit-impaired)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>350</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 (lifetime ECL, credit-impaired)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>9617</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>7593</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2886</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>3332</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Derived ratios</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>NPL ratio (Stage 3 gross / total gross)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>7.92%</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>5.77%</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>3.19%</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>1.73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 coverage ratio (Stage 3 impairment / Stage 3 gross)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>14.73%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>10.94%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>13.79%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>6.21%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>11.99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="320" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Kuwait Finance House Plc's (formerly Ahli United Bank (UK) PLC's) own Annual Report and Financial Statements, Note 13 'Financing receivables' (FY2024-FY2025) / 'Loans and advances' (FY2021-FY2023), IFRS 9 stage-by-stage gross carrying amount and impairment allowance tables:
+FY2025/FY2024 (own): Annual Report and Financial Statements 2025, p.51-52 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023 (own): Annual Report and Financial Statements 2023, p.47-48 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQxNzM5MjkxNGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 (own) / FY2021 (comparative, used here in place of AR2021's own Note since it discloses the same IFRS 9 stage granularity): Annual Report and Financial Statements 2022, p.45-47 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+ENTITY NOTE: Kuwait Finance House Plc (FRN 131818, Companies House 00877859) was formerly Ahli United Bank (UK) PLC - renamed following its 2024 conversion to a Shariah-compliant (Islamic) bank under new ownership (Kuwait Finance House Group), confirmed by the FY2024/FY2025 Annual Reports' own Shariah Supervisory Board report describing 'the recent conversion of the Bank'. This is a genuine, disclosed business-model change, not a data anomaly: FY2021-FY2023 use conventional banking terminology (Loans and advances, Interest income/expense/receivable/payable); FY2024-FY2025 use Islamic-finance terminology (Financing receivables, Returns receivable/payable) for the functionally equivalent line items, kept as each year's own originally-printed labels rather than forced into a single common wording. Reports in USD'000 (Bank/solo basis) - all Companies House filings are fully scanned/image-only, transcribed via targeted page-image reads, not full-document OCR. Kept in native USD (not converted to GBP), consistent with sibling USD-reporting banks built in this same batch (e.g. Itau BBA International plc).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kuwait Finance House Plc — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>CET1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>19.9%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="280" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
-FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kuwait Finance House Plc — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>USD m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>325.3</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>316.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>323.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: No Additional Tier 1 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout. A small Tier 2 balance ($799k) exists only in FY2021 (see Total Capital), fully amortised/repaid by FY2022 onward.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="280" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
-FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kuwait Finance House Plc — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>19.9%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: No Additional Tier 1 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout. A small Tier 2 balance ($799k) exists only in FY2021 (see Total Capital), fully amortised/repaid by FY2022 onward.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="280" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
-FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3543,7 +7490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Total Capital</t>
+          <t>Kuwait Finance House Plc — CET1 Capital</t>
         </is>
       </c>
     </row>
@@ -3589,7 +7536,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital / Own Funds</t>
+          <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
@@ -3605,7 +7552,7 @@
         <v>304.5</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>319.8</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" ht="280" customHeight="1">
@@ -3647,7 +7594,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Total Capital Ratio</t>
+          <t>Kuwait Finance House Plc — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -3693,7 +7640,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
+          <t>CET1 ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3718,7 +7665,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
     </row>
@@ -3761,7 +7708,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Total RWAs</t>
+          <t>Kuwait Finance House Plc — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -3807,29 +7754,29 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount (calculated)</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1618.4</v>
+        <v>325.3</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>1649.3</v>
+        <v>316.7</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1666</v>
+        <v>323.2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1530.2</v>
+        <v>304.5</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1421.3</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Total RWAs are NOT directly disclosed in the source - calculated as Own Funds / Total Capital ratio for each year (see sheet-level source note). Treat as an approximation consistent with the source's own rounded percentages, not a directly-quoted figure.</t>
+          <t>Note: No Additional Tier 1 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout. A small Tier 2 balance ($799k) exists only in FY2021 (see Total Capital), fully amortised/repaid by FY2022 onward.</t>
         </is>
       </c>
     </row>

--- a/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
+++ b/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
@@ -4035,7 +4035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -4173,7 +4173,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Financial investments</t>
+          <t>Total financial investments</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -4195,501 +4195,633 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments</t>
+          <t>Financial investments - GCC government bonds/Sukuk (sovereign debt, amortised cost)</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>6952</v>
+        <v>99438</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>41151</v>
+        <v>67285</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>34717</v>
+        <v>164797</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>56979</v>
+        <v>222762</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>18040</v>
+        <v>194626</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Investment in joint venture</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
+          <t>Financial investments - Issued by banks and other financial institutions (amortised cost)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>141838</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>139475</v>
+      </c>
       <c r="D10" s="6" t="n">
-        <v>64</v>
+        <v>248594</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>60</v>
+        <v>147794</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>69</v>
+        <v>145262</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Investments in group undertakings</t>
+          <t>Financial investments - Issued by corporate bodies (amortised cost)</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>34</v>
+        <v>138332</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>32</v>
+        <v>146784</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>32</v>
+        <v>196476</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>47</v>
+        <v>164546</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>52</v>
+        <v>17308</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Premises and equipment</t>
+          <t>Financial investments - ECL impairment provision on amortised-cost investments (amortised cost)</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>2436</v>
+        <v>-129</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>4058</v>
+        <v>-100</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5311</v>
+        <v>-747</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>6031</v>
+        <v>-709</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>10618</v>
+        <v>-358</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets</t>
+          <t>Financial investments - Investments not directly quoted (FVTPL)</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>5599</v>
-      </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
+        <v>143</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>516</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>420</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>928</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Investment property</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
+          <t>Financial investments - Private equity investments at net asset value (FVOCI)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>40374</v>
+      </c>
       <c r="C14" s="6" t="n">
-        <v>278</v>
+        <v>44059</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>316</v>
+        <v>49142</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>354</v>
+        <v>47772</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>392</v>
+        <v>54378</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Returns receivable and similar assets / Interest receivable and other assets</t>
+          <t>Derivative financial instruments</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>19310</v>
+        <v>6952</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>24659</v>
+        <v>41151</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>15409</v>
+        <v>34717</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>12994</v>
+        <v>56979</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>8682</v>
+        <v>18040</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Current tax asset</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>1233</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>1769</v>
-      </c>
+          <t>Investment in joint venture</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n">
-        <v>1515</v>
+        <v>64</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>274</v>
+        <v>60</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>507</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Deferred tax asset</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
+          <t>Investments in group undertakings</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>32</v>
+      </c>
       <c r="E17" s="6" t="n">
-        <v>87</v>
-      </c>
-      <c r="F17" s="6" t="n"/>
+        <v>47</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Retirement benefit scheme</t>
+          <t>Premises and equipment</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3509</v>
+        <v>2436</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3105</v>
+        <v>4058</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>3347</v>
+        <v>5311</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>24381</v>
+        <v>6031</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>46616</v>
+        <v>10618</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>2576896</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>2737527</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>2923898</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>2835743</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>2996510</v>
-      </c>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>5599</v>
+      </c>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Investment property</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
+      <c r="C20" s="6" t="n">
+        <v>278</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>316</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>354</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>392</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Deposits from banks</t>
+          <t>Returns receivable and similar assets / Interest receivable and other assets</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>23106</v>
+        <v>19310</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>59630</v>
+        <v>24659</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>11164</v>
+        <v>15409</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>86543</v>
+        <v>12994</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>84073</v>
+        <v>8682</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Customer deposits</t>
+          <t>Current tax asset</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>2149033</v>
+        <v>1233</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>2259618</v>
+        <v>1769</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2509823</v>
+        <v>1515</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>2359144</v>
+        <v>274</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>2515820</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Borrowings under repurchase agreements</t>
+          <t>Deferred tax asset</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="F23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments</t>
+          <t>Retirement benefit scheme</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>12582</v>
+        <v>3509</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>4694</v>
+        <v>3105</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>13253</v>
+        <v>3347</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>16006</v>
+        <v>24381</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>21690</v>
+        <v>46616</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Returns payable and similar liabilities / Interest payable and other liabilities</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>57607</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>62898</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>53969</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>26000</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>27532</v>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2576896</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2737527</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2923898</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>2835743</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>2996510</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Deferred tax liability</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>1959</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>3408</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>1935</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>8303</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>14663</v>
-      </c>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Subordinated liabilities</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
+          <t>Deposits from banks</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>23106</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>59630</v>
+      </c>
       <c r="D27" s="6" t="n">
-        <v>0</v>
+        <v>11164</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>9462</v>
+        <v>86543</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>9983</v>
+        <v>84073</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>2244287</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>2390248</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>2590144</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>2505458</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>2673761</v>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Customer deposits</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>2149033</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>2259618</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>2509823</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>2359144</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>2515820</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Equity</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Borrowings under repurchase agreements</t>
         </is>
       </c>
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="6" t="n"/>
       <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
+      <c r="F29" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Ordinary share capital</t>
+          <t>Derivative financial instruments</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>200080</v>
+        <v>12582</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>200080</v>
+        <v>4694</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>200080</v>
+        <v>13253</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>200080</v>
+        <v>16006</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>200080</v>
+        <v>21690</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t>Returns payable and similar liabilities / Interest payable and other liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>57607</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>62898</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>53969</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>27532</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax liability</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>1959</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>3408</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>1935</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>8303</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>14663</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Subordinated liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>9462</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>9983</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2244287</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>2390248</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2590144</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>2505458</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>2673761</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Ordinary share capital</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>200080</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>200080</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>200080</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>200080</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>200080</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
           <t>Reserves</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B37" s="6" t="n">
         <v>132529</v>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C37" s="6" t="n">
         <v>147199</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D37" s="6" t="n">
         <v>133674</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E37" s="6" t="n">
         <v>130205</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F37" s="6" t="n">
         <v>122669</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B38" s="5" t="n">
         <v>332609</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C38" s="5" t="n">
         <v>347279</v>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D38" s="5" t="n">
         <v>333754</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E38" s="5" t="n">
         <v>330285</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F38" s="5" t="n">
         <v>322749</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Total liabilities and equity</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B39" s="5" t="n">
         <v>2576896</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C39" s="5" t="n">
         <v>2737527</v>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D39" s="5" t="n">
         <v>2923898</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E39" s="5" t="n">
         <v>2835743</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F39" s="5" t="n">
         <v>2996510</v>
       </c>
     </row>
-    <row r="35" ht="420" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="41" ht="520" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Kuwait Finance House Plc's (formerly Ahli United Bank (UK) PLC's) own Annual Report and Financial Statements, from Companies House filings:
 FY2025: Bank Balance Sheet p.27, Consolidated Statement of Income p.24, Consolidated Statement of Comprehensive Income p.25, Bank Statement of Changes in Equity p.30-31 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
@@ -4698,13 +4830,19 @@
 FY2022: Bank Balance Sheet p.23, Consolidated Statement of Income p.20, Consolidated Statement of Comprehensive Income p.21, Bank Statement of Changes in Equity p.27 (own report) - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2021: Bank Balance Sheet p.17, Consolidated Statement of Income (unpaginated, follows p.13), Consolidated Statement of Comprehensive Income p.15, Bank Statement of Changes in Equity p.21 (own report) - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM0MTg2NjEyNWFkaXF6a2N4/document?format=pdf&amp;download=0
 ENTITY NOTE: Kuwait Finance House Plc (FRN 131818, Companies House 00877859) was formerly Ahli United Bank (UK) PLC - renamed following its 2024 conversion to a Shariah-compliant (Islamic) bank under new ownership (Kuwait Finance House Group), confirmed by the FY2024/FY2025 Annual Reports' own Shariah Supervisory Board report describing 'the recent conversion of the Bank'. This is a genuine, disclosed business-model change, not a data anomaly: FY2021-FY2023 use conventional banking terminology (Loans and advances, Interest income/expense/receivable/payable); FY2024-FY2025 use Islamic-finance terminology (Financing receivables, Returns receivable/payable) for the functionally equivalent line items, kept as each year's own originally-printed labels rather than forced into a single common wording. Reports in USD'000 (Bank/solo basis) - all Companies House filings are fully scanned/image-only, transcribed via targeted page-image reads, not full-document OCR. Kept in native USD (not converted to GBP), consistent with sibling USD-reporting banks built in this same batch (e.g. Itau BBA International plc).
-BASIS NOTE: this entity takes the exemption in s.408 Companies Act 2006 and does not present a standalone Bank/solo income statement in any year - only a Consolidated (Group) income statement and comprehensive income statement are published, each year's own Bank Balance Sheet page noting the Bank's own profit-after-tax figure separately (used here to build the Statement of Changes in Equity, which the Bank DOES publish on a solo basis every year). The Balance Sheet and Statement of Changes in Equity sheets in this workbook are therefore Bank/solo basis (consistent with the existing Cash Flow Statement sheet), while the Profit &amp; Loss sheet is necessarily Consolidated (Group) basis - the only income statement this entity discloses. Group and Bank scope differ only immaterially here (a small non-trading subsidiary), so the two bases are not directly comparable line-by-line but both are genuine, source-disclosed figures, not derived or estimated.</t>
+BASIS NOTE: this entity takes the exemption in s.408 Companies Act 2006 and does not present a standalone Bank/solo income statement in any year - only a Consolidated (Group) income statement and comprehensive income statement are published, each year's own Bank Balance Sheet page noting the Bank's own profit-after-tax figure separately (used here to build the Statement of Changes in Equity, which the Bank DOES publish on a solo basis every year). The Balance Sheet and Statement of Changes in Equity sheets in this workbook are therefore Bank/solo basis (consistent with the existing Cash Flow Statement sheet), while the Profit &amp; Loss sheet is necessarily Consolidated (Group) basis - the only income statement this entity discloses. Group and Bank scope differ only immaterially here (a small non-trading subsidiary), so the two bases are not directly comparable line-by-line but both are genuine, source-disclosed figures, not derived or estimated.
+FINANCIAL INVESTMENTS BREAKDOWN: the 'Financial investments - ...' sub-rows below the headline 'Total financial investments' line are transcribed from Note 14 'Financial investments' (Note 14(a) 'Financial Investments by category' and Note 14(b) ECL impairment summary) of each year's own Notes to the Financial Statements, which splits the balance both by measurement basis (amortised cost / fair value through profit or loss (FVTPL) / fair value through other comprehensive income (FVOCI)) and, within the amortised-cost bucket, by issuer type (GCC government bonds/Sukuk and similar instruments; issued by banks and other financial institutions; issued by corporate bodies):
+FY2025/FY2024 (own): Annual Report and Financial Statements 2025, Note 14, p.52 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023 (own) / FY2022 (comparative): Annual Report and Financial Statements 2023, Note 14, p.48 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQxNzM5MjkxNGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 (own) / FY2021 (comparative): Annual Report and Financial Statements 2022, Note 14, p.47 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2021 (own): Annual Report and Financial Statements 2021, Note 14, p.38 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM0MTg2NjEyNWFkaXF6a2N4/document?format=pdf&amp;download=0
+The three amortised-cost issuer-type sub-rows are gross carrying amounts (Note 14(a)'s own 'Quoted investments' lines); the 'ECL impairment provision' sub-row is that same note's single aggregate impairment allowance (Note 14(b), not broken down by issuer), so the four amortised-cost sub-rows plus the FVTPL and FVOCI sub-rows sum exactly to that year's headline 'Total financial investments' line every year. GCC government bonds and debt securities are labelled 'GCC government Sukuk and similar instruments' from FY2024 onward, reflecting the FY2024 Shariah conversion (see ENTITY_NOTE) - the same amortised-cost sovereign-debt line, kept under each year's own originally-printed wording rather than forced into a single common label.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A41:F41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
+++ b/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
@@ -3033,7 +3033,7 @@
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
         </is>
       </c>
     </row>
@@ -3330,29 +3330,41 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted exposure amount (calculated)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1618.4</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1649.3</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1666</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>1530.2</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1421.3</v>
+          <t>Total risk-weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Total RWAs are NOT directly disclosed in the source - calculated as Own Funds / Total Capital ratio for each year (see sheet-level source note). Treat as an approximation consistent with the source's own rounded percentages, not a directly-quoted figure.</t>
+          <t>Note: NOT PUBLICLY DISCLOSED. Kuwait Finance House Plc does not publish a total risk-weighted exposure amount. The Pillar 3 appendix gives ratios and Own Funds only.
+WITHDRAWAL RECORD (2026-09-16). This sheet previously carried FY2025 1,618.4; FY2024 1,649.3; FY2023 1,666.0; FY2022 1,530.2; FY2021 1,421.3 (USD m), each back-solved as Own Funds divided by that year's Total Capital ratio. They were withdrawn on the project owner's decision: the ratio is published rounded to one decimal place, so the quotient carries a materially wider band than its four significant figures imply, and a computed value in a disclosure column reads as a disclosure. The arithmetic is preserved in this build script as TOTAL_RWA_CALC_WITHDRAWN so the removal stays auditable.
+SEE THE RWA BREAKDOWN SHEET FOR WHAT THE BANK DOES DISCLOSE. That sheet is NOT affected by this withdrawal and is a different calculation: the Pillar 3 appendix publishes the minimum Pillar 1 CAPITAL REQUIREMENT by risk category every year, and those disclosed components are multiplied by 12.5 (the inverse of the fixed 8% own-funds requirement) to state them as RWA-equivalents. That is a unit conversion of published figures against a regulatory constant, not a back-solve from a rounded ratio. As a cross-check, the two approaches agreed to within 0.15% in every year before this withdrawal (e.g. FY2025 1,618.4 against 1,617.7), which is why the breakdown's totals remain sound while the division above does not.</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3375,7 @@
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3568,7 @@
 FY2025/FY2024: p.83-84 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.
 RWA BREAKDOWN METHOD: the source discloses 'The minimum capital requirements under Pillar 1' by risk category every year (Credit and counterparty risk capital requirement (SA); Market risk capital requirement; Credit value adjustment capital requirement; Operational risk capital requirement (BIA)) but never a category-level RWA figure directly. Each category's RWA-equivalent is calculated here as capital requirement / 8% (i.e. x12.5), the standard Basel III relationship between capital requirement and RWA under the Standardised Approach. The resulting Total RWAs (this sheet's own component sum) differs from the Total RWAs sheet's Own-Funds/Total-Capital-ratio-based calculation by under 0.2% every year - both are legitimate derivations from disclosed figures, neither is a directly-quoted 'Total RWAs' line item, and the small gap is an immaterial reconciliation-methodology difference, not a data error.</t>
         </is>
       </c>
@@ -3671,7 +3683,7 @@
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3797,7 @@
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3911,7 @@
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4028,7 @@
 FY2025/FY2024: p.n/a - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7712,7 @@
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7826,7 @@
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
         </is>
       </c>
     </row>
@@ -7925,7 +7937,7 @@
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure) - calculated here as Own Funds / Total Capital ratio for each year, flagged as calculated rather than directly quoted.</t>
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
         </is>
       </c>
     </row>

--- a/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
+++ b/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2944,14 +2945,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Tier 1 Ratio</t>
+          <t>Kuwait Finance House Plc — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>USD m</t>
         </is>
       </c>
     </row>
@@ -2990,33 +2991,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>19.9%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>319</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -3052,7 +3043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3066,14 +3057,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Total Capital</t>
+          <t>Kuwait Finance House Plc — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3112,27 +3103,44 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital / Own Funds</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>325.3</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>316.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>323.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>319.8</v>
-      </c>
-    </row>
-    <row r="6" ht="280" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>19.9%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: No Additional Tier 1 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout. A small Tier 2 balance ($799k) exists only in FY2021 (see Total Capital), fully amortised/repaid by FY2022 onward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
@@ -3143,8 +3151,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3170,14 +3179,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Total Capital Ratio</t>
+          <t>Kuwait Finance House Plc — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>USD m</t>
         </is>
       </c>
     </row>
@@ -3216,33 +3225,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>19.9%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22.5%</t>
-        </is>
+          <t>Total capital / Own Funds</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>319.8</v>
       </c>
     </row>
     <row r="6" ht="280" customHeight="1">
@@ -3265,6 +3264,120 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>19.9%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="280" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
+FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3388,7 +3501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3576,120 +3689,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A10:F10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kuwait Finance House Plc — Leverage Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Leverage ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>13.7%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>11.9%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>12.3%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>10.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="280" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
-FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3715,7 +3714,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — LCR</t>
+          <t>Kuwait Finance House Plc — Leverage Ratio</t>
         </is>
       </c>
     </row>
@@ -3761,32 +3760,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Liquidity Coverage Ratio</t>
+          <t>Leverage ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>592.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>385.4%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>662.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>392.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>486.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3828,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — NSFR</t>
+          <t>Kuwait Finance House Plc — LCR</t>
         </is>
       </c>
     </row>
@@ -3875,32 +3874,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio</t>
+          <t>Liquidity Coverage Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>139.0%</t>
+          <t>592.3%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>385.4%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>133.0%</t>
+          <t>662.5%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>392.5%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>136.2%</t>
+          <t>486.4%</t>
         </is>
       </c>
     </row>
@@ -3924,6 +3923,120 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>139.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>119.4%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>133.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>127.4%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>136.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="280" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
+FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7629,7 +7742,7 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="86" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -7640,21 +7753,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — CET1 Capital</t>
+          <t>Kuwait Finance House Plc — KM1 Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>Not applicable - this bank publishes Pillar 3 disclosures every year (as a signed appendix inside its Annual Report and Financial Statements) but does not use the UK KM1 key-metrics template in any of them. Its own 'Key Metrics' block is a five-row ratio summary, which fails the template's row-set test. See the source note for the full evidence and for what the bank does disclose instead.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -7686,33 +7799,27 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>325.3</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>316.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>323.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="6" ht="280" customHeight="1">
+          <t>Not applicable - the UK KM1 key-metrics template is not used in any year (see note below)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="460" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
-FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
+          <t>NOT APPLICABLE - Kuwait Finance House Plc does not use the UK KM1 key-metrics template in any year. This is an affirmative finding read off the documents, not the result of a search that failed to find a table.
+WHAT THE BANK DOES PUBLISH. A Pillar 3 disclosure exists for every year in this workbook, but not as a standalone document: it is printed as a signed appendix inside the Annual Report and Financial Statements filed at Companies House, headed 'APPENDIX : PILLAR 3 DISCLOSURES (UNAUDITED)' and dated at the top of each page. Verified page by page in the FY2025 filing (printed folios 83-85) and, under the bank's former name Ahli United Bank (UK) PLC, in the FY2022 filing (printed folio 72).
+WHY IT IS NOT THE TEMPLATE (map rule 8, the ROW-SET TEST). The appendix opens with a block headed 'Key Metrics - Key capital and liquidity metrics at 31 December are:' and that block is FIVE ROWS, all of them ratios, in this order: Total Capital ratio, Common Equity Tier 1 (CET1) Capital Ratio, Leverage Ratio, Liquidity Coverage Ratio, Net Stable Funding Ratio. It carries two columns (the reporting year and the prior year) and no row numbers. Everything else the UK KM1 template requires is simply absent: no CET1, Tier 1 or Total capital AMOUNT rows, no total risk-weighted exposure amount, no Tier 1 ratio, none of the UK 7a-7d SREP rows, no capital conservation or countercyclical buffer rows, no combined buffer requirement, no leverage exposure measure, and no LCR or NSFR component build-ups (rows 15-16, UK 16a/16b, 18-19). A five-row ratio summary is a different and shorter table, not an unnumbered KM1, and mapping it onto template row numbers would invent a correspondence the bank never published.
+WHAT IS ADJACENT TO IT, and why it still is not KM1. The same appendix does print a 'Capital Structure and Own Funds' table (a CET1 build-up ending in Own Funds) and an 'Own Funds requirements' table (the minimum Pillar 1 capital requirement by risk category). Those are CC1-like and OV1-like disclosures, and this workbook already uses them - they are the source for the CET1 Capital, Tier 1 Capital, Total Capital and RWA Breakdown sheets. They are not the KM1 template and are not reproduced here as one.
+THE FIVE RATIOS THEMSELVES ARE ALREADY IN THIS WORKBOOK, on the CET1 Ratio, Total Capital Ratio, Leverage Ratio, LCR and NSFR sheets, each with its own citation. Nothing is lost by this sheet carrying no rows.
+AN EXTRACTION CAVEAT WORTH RECORDING (map rules 13 and 15). Every Companies House filing for this company is a whole-document scan: pdftotext returns 91 characters for the entire 91-page FY2025 filing, and pdfimages confirms one full-page CCITT bitmap per page. Any keyword search over these documents therefore returns zero for everything, and a zero from that instrument says nothing whatever about the bank. The finding above was made by RENDERING the appendix pages at 150dpi and reading them by eye, which is the only instrument that works on this filing set.
+LATEST-EDITION CHECK (required by the KM1 map), performed 2026-09-17. The bank's own web presence, kfhuk.com, is a single-page holding site: its robots.txt points at /sitemap.xml, and that sitemap contains exactly one URL (/lander). There is no investor, results or regulatory-disclosures section to check, and no Pillar 3 document is published on the bank's website at all - which is consistent with, and explains, the disclosure living inside the Companies House filing. The newest filing available is the Annual Report and Financial Statements 2025 (FY2025), which is already this workbook's most recent year. NONE NEWER EXISTS; this workbook is not an edition behind.
+NOTE ON kfh.co.uk, recorded so a later session does not repeat the mistake: that domain is NOT this bank. It belongs to Kinleigh Folkard &amp; Hayward, a London estate agency, and it resolves and serves a normal site - so an automated check that assumed the obvious domain would have read an unrelated company's pages as this bank's.
+ENTITY NOTE: Kuwait Finance House Plc (FRN 131818, Companies House 00877859) was formerly Ahli United Bank (UK) PLC - renamed following its 2024 conversion to a Shariah-compliant (Islamic) bank under new ownership (Kuwait Finance House Group), confirmed by the FY2024/FY2025 Annual Reports' own Shariah Supervisory Board report describing 'the recent conversion of the Bank'. This is a genuine, disclosed business-model change, not a data anomaly: FY2021-FY2023 use conventional banking terminology (Loans and advances, Interest income/expense/receivable/payable); FY2024-FY2025 use Islamic-finance terminology (Financing receivables, Returns receivable/payable) for the functionally equivalent line items, kept as each year's own originally-printed labels rather than forced into a single common wording. Reports in USD'000 (Bank/solo basis) - all Companies House filings are fully scanned/image-only, transcribed via targeted page-image reads, not full-document OCR. Kept in native USD (not converted to GBP), consistent with sibling USD-reporting banks built in this same batch (e.g. Itau BBA International plc).</t>
         </is>
       </c>
     </row>
@@ -7744,14 +7851,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — CET1 Ratio</t>
+          <t>Kuwait Finance House Plc — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>USD m</t>
         </is>
       </c>
     </row>
@@ -7790,33 +7897,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>CET1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>19.9%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>319</v>
       </c>
     </row>
     <row r="6" ht="280" customHeight="1">
@@ -7844,7 +7941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7858,14 +7955,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Tier 1 Capital</t>
+          <t>Kuwait Finance House Plc — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -7904,34 +8001,37 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>325.3</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>316.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>323.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: No Additional Tier 1 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout. A small Tier 2 balance ($799k) exists only in FY2021 (see Total Capital), fully amortised/repaid by FY2022 onward.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="280" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>CET1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>19.9%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="280" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
@@ -7942,9 +8042,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
+++ b/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
@@ -1697,6 +1697,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3448,34 +3449,36 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not publicly disclosed — see RWA Breakdown (derived x12.5)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not publicly disclosed — see RWA Breakdown (derived x12.5)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not publicly disclosed — see RWA Breakdown (derived x12.5)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not publicly disclosed — see RWA Breakdown (derived x12.5)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not publicly disclosed — see RWA Breakdown (derived x12.5)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: NOT PUBLICLY DISCLOSED. Kuwait Finance House Plc does not publish a total risk-weighted exposure amount. The Pillar 3 appendix gives ratios and Own Funds only.
+          <t>Note: NOT PUBLICLY DISCLOSED, AND THE RWA BREAKDOWN SHEET'S TOTAL IS NOT A CONTRADICTION OF THAT - it is a derivation, and this note says exactly what the Bank does and does not print.
+WHAT THE BANK PRINTS, re-read end to end 2026-09-18 from the FY2025 Annual Report's own Appendix: Pillar 3 Disclosures (unaudited), printed folios 83-89. (i) A five-row 'Key Metrics' block on printed p.83: Total Capital ratio, CET1 Capital Ratio, Leverage Ratio, Liquidity Coverage Ratio, Net Stable Funding Ratio. No RWA row. (ii) A 'Capital Structure and Own Funds' table on the same page: a CET1 component build-up ending in Own Funds. No RWA row. (iii) 'The minimum capital requirements under Pillar 1' on printed p.84: CAPITAL REQUIREMENTS by risk category, footing to a Total Pillar 1 capital requirement of US$129,413k (2025) and US$131,855k (2024). Again no RWA. (iv) Credit-quality-step exposure tables, counterparty credit risk, impaired exposures, asset encumbrance and remuneration across printed pp.85-89 - none of which states an RWA either.
+THE ZERO IS A FACT ABOUT THE DOCUMENT, NOT ABOUT THE EXTRACTION. These filings are whole-document image scans (go-tiff2pdf, no text layer at all), so the appendix was rendered at 200dpi and read. The phrases 'risk weighted' and 'risk-weighted' occur ZERO times across all seven appendix pages, while the same extraction returns the appendix's 'Risk Weight' column headers, its capital-requirement tables in full, and every narrative section named above. The Bank's vocabulary for this concept is 'capital requirement' and 'Risk Weight'; it never states a risk-weighted total.
 WITHDRAWAL RECORD (2026-09-16). This sheet previously carried FY2025 1,618.4; FY2024 1,649.3; FY2023 1,666.0; FY2022 1,530.2; FY2021 1,421.3 (USD m), each back-solved as Own Funds divided by that year's Total Capital ratio. They were withdrawn on the project owner's decision: the ratio is published rounded to one decimal place, so the quotient carries a materially wider band than its four significant figures imply, and a computed value in a disclosure column reads as a disclosure. The arithmetic is preserved in this build script as TOTAL_RWA_CALC_WITHDRAWN so the removal stays auditable.
 SEE THE RWA BREAKDOWN SHEET FOR WHAT THE BANK DOES DISCLOSE. That sheet is NOT affected by this withdrawal and is a different calculation: the Pillar 3 appendix publishes the minimum Pillar 1 CAPITAL REQUIREMENT by risk category every year, and those disclosed components are multiplied by 12.5 (the inverse of the fixed 8% own-funds requirement) to state them as RWA-equivalents. That is a unit conversion of published figures against a regulatory constant, not a back-solve from a rounded ratio. As a cross-check, the two approaches agreed to within 0.15% in every year before this withdrawal (e.g. FY2025 1,618.4 against 1,617.7), which is why the breakdown's totals remain sound while the division above does not.</t>
         </is>
@@ -3528,7 +3531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Derived (x12.5) from the Pillar 3 appendix's own 'minimum capital requirements under Pillar 1' table by risk category - RWAs are not directly disclosed as a category-level figure, but the underlying capital requirement components are. USD'000.</t>
+          <t>DERIVED, NOT DISCLOSED. The Bank publishes no RWA figure - neither by category nor in total (appendix re-read end to end 2026-09-18; see the Total RWAs sheet's note). Every figure on this sheet is the Pillar 3 appendix's own disclosed 'minimum capital requirements under Pillar 1' by risk category, multiplied by 12.5 to state it as an RWA-equivalent. USD'000.</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3658,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Total RWAs (derived from disclosed Pillar 1 capital requirement components)</t>
+          <t>Total RWAs - DERIVED here (x12.5) from the disclosed Pillar 1 capital requirement components above; the Bank publishes no total RWA figure of its own</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -4130,7 +4133,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed any year - consistent with a small UK bank subsidiary that is not itself a resolution entity.</t>
+          <t>Note: Not publicly disclosed any year. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): this note previously read 'consistent with a small UK bank subsidiary that is not itself a resolution entity' - a plausibility argument rather than evidence. The Bank of England's own 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures - the 2023, 2024, 2025 and 2026 editions at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt; - contain, in the BoE's own words, 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated'. KFH is named in none of the four editions. As a UK subsidiary of Kuwait Finance House K.S.C.P., whose resolution entity is not incorporated in the UK, that absence is exactly what the scope sentence predicts, and the reasoning in this note is now sourced rather than assumed. The BoE publishes the REQUIREMENT, not the ratio, so nothing from that table is transcribed here - it establishes that there was nothing for the Bank to disclose.</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="86" customWidth="1" min="1" max="1"/>
@@ -7799,17 +7802,101 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable - the UK KM1 key-metrics template is not used in any year (see note below)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="460" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+          <t>UK KM1 key-metrics template</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published — the template is not used</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published — the template is not used</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published — the template is not used</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published — the template is not used</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published — the template is not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Pillar 3 disclosures published by the Bank (signed Appendix inside each Annual Report)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Published every year, but contain no KM1</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Published every year, but contain no KM1</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Published every year, but contain no KM1</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Published every year, but contain no KM1</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Published every year, but contain no KM1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>The Bank's own five-row 'Key Metrics' block (Total Capital ratio, CET1 ratio, Leverage Ratio, LCR, NSFR), printed in its place</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable as a KM1 — fails the row-set test</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable as a KM1 — fails the row-set test</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable as a KM1 — fails the row-set test</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable as a KM1 — fails the row-set test</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable as a KM1 — fails the row-set test</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="460" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>NOT APPLICABLE - Kuwait Finance House Plc does not use the UK KM1 key-metrics template in any year. This is an affirmative finding read off the documents, not the result of a search that failed to find a table.
 WHAT THE BANK DOES PUBLISH. A Pillar 3 disclosure exists for every year in this workbook, but not as a standalone document: it is printed as a signed appendix inside the Annual Report and Financial Statements filed at Companies House, headed 'APPENDIX : PILLAR 3 DISCLOSURES (UNAUDITED)' and dated at the top of each page. Verified page by page in the FY2025 filing (printed folios 83-85) and, under the bank's former name Ahli United Bank (UK) PLC, in the FY2022 filing (printed folio 72).
@@ -7825,7 +7912,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
+++ b/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
@@ -4106,27 +4106,27 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – no MREL above MCR: KFH Plc absent from BoE 'External MRELs' lists 2023–26, which name every UK resolution entity with MREL above MCR; AR FY2025 (incl. Pillar 3) has none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – no MREL above MCR: KFH Plc absent from BoE 'External MRELs' lists 2023–26, which name every UK resolution entity with MREL above MCR; AR FY2024 (incl. Pillar 3) has none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – no MREL above MCR: KFH Plc absent from BoE 'External MRELs' lists 2023–26, which name every UK resolution entity with MREL above MCR; AR FY2023 (incl. Pillar 3) has none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in KFH Plc Annual Report FY2022 or its Pillar 3 appendix (CH scan, OCR 2026-09-19).</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no MREL figure in KFH Plc Annual Report FY2021 or its Pillar 3 appendix (CH scan, OCR 2026-09-19).</t>
         </is>
       </c>
     </row>

--- a/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
+++ b/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="45" customHeight="1">
+    <row r="39" ht="91" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Note: Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) converted to a Shariah-compliant (Islamic) bank during FY2024 under new ownership - see the Balance Sheet sheet's ENTITY NOTE. Figures are US$, not converted to GBP (native-currency presentation, consistent with sibling USD-reporting banks in this batch). Balance Sheet and Statement of Changes in Equity are Bank/solo basis; Profit &amp; Loss is necessarily Consolidated (Group) basis - this entity does not publish a standalone Bank income statement (see the Balance Sheet sheet's BASIS NOTE) - so the equity-changes block above uses the equity sheet's own Bank-basis comprehensive income, not the Group P&amp;L's OCI total. Total RWAs is independently derived two ways (Own Funds/Total Capital ratio on the Total RWAs sheet; summed Pillar 1 capital requirement components x12.5 on the RWA Breakdown sheet) since no single RWA figure is directly disclosed - both agree within 0.2%. Figures are duplicated from the detail sheets for at-a-glance trend viewing.</t>
@@ -3011,7 +3011,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: No Additional Tier 1 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout. A small Tier 2 balance ($799k) exists only in FY2021 (see Total Capital), fully amortised/repaid by FY2022 onward.</t>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: No Additional Tier 1 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout. A small Tier 2 balance ($799k) exists only in FY2021 (see Total Capital), fully amortised/repaid by FY2022 onward.</t>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="312" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: NOT PUBLICLY DISCLOSED, AND THE RWA BREAKDOWN SHEET'S TOTAL IS NOT A CONTRADICTION OF THAT - it is a derivation, and this note says exactly what the Bank does and does not print.
@@ -3703,7 +3703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3792,8 +3792,17 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="280" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="5" ht="208" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: GA-026 LEVERAGE BASIS (2026-10-10): ONE BASIS, UNDECLARED - and on this bank's disclosure the question is not answerable from the documents. KFH publishes no standalone Pillar 3 and no UK KM1 template. What exists is an "APPENDIX : PILLAR 3 DISCLOSURES (UNAUDITED)" inside each year's own Annual Report, whose 'Key Metrics' table prints a short list of ratios and nothing else. Read at 300 dpi from the FY2025 Annual Report, PDF page 85 = printed folio 83: Total Capital ratio 20.1% / 19.2%; CET1 Capital Ratio 20.1% / 19.2%; Leverage Ratio 14.2% / 13.7%; LCR 592.3% / 385.4%; NSFR 139.0% / 119.4%.
+WHY IT IS NOT DETERMINABLE. The caption is the bare words 'Leverage Ratio' with no qualifier. There is no row 24 / UK-24a / UK-24b / UK-25c, no LR2 or LRSum template, and - decisively - NO EXPOSURE MEASURE IS PRINTED AT ALL, so there is no denominator to inspect for a central-bank deduction line. That is the test that settled Bank Sepah International, Jordan International Bank and United National Bank (a printed reconciliation deducting nothing) and its mirror at Bank of Ceylon UK (an explicit Bank of England deduction); here the test cannot be run, because the bank publishes the ratio and withholds both of its terms. The same appendix withholds the RWA figure for the same reason (see the Total RWAs sheet, where a back-solved series was withdrawn on 2026-09-16), so this is a consistent feature of KFH's disclosure, not an oversight on one row. NOTHING IS BACK-SOLVED HERE: no exposure measure is inferred from the ratio and the capital figure, and no basis is asserted.
+SCOPE. The two-basis UK presentation is effective only for periods from 1 January 2022; KFH never adopted the UK KM1 template in any year covered. A normalised phrase scan (text joined across line breaks before matching, so a wrapped phrase cannot hide) finds no 'excluding/including claims on central banks' wording in the source. Note that these Annual Reports are IMAGE SCANS at Companies House with no usable text layer, so that scan rests on OCR for navigation and on the 300 dpi render for every figure quoted above - per project convention the render, not the OCR, is the reading. The FY2025 document is Companies House filing MzUyMTMwODAyMGFkaXF6a2N4 (91 pages).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
@@ -3804,8 +3813,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4130,14 +4140,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="91" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed any year. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): this note previously read 'consistent with a small UK bank subsidiary that is not itself a resolution entity' - a plausibility argument rather than evidence. The Bank of England's own 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures - the 2023, 2024, 2025 and 2026 editions at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt; - contain, in the BoE's own words, 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated'. KFH is named in none of the four editions. As a UK subsidiary of Kuwait Finance House K.S.C.P., whose resolution entity is not incorporated in the UK, that absence is exactly what the scope sentence predicts, and the reasoning in this note is now sourced rather than assumed. The BoE publishes the REQUIREMENT, not the ratio, so nothing from that table is transcribed here - it establishes that there was nothing for the Bank to disclose.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="156" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
@@ -4163,7 +4173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -4948,7 +4958,7 @@
         <v>2996510</v>
       </c>
     </row>
-    <row r="41" ht="520" customHeight="1">
+    <row r="41" ht="409" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Kuwait Finance House Plc's (formerly Ahli United Bank (UK) PLC's) own Annual Report and Financial Statements, from Companies House filings:
@@ -4961,7 +4971,14 @@
 BASIS NOTE: this entity takes the exemption in s.408 Companies Act 2006 and does not present a standalone Bank/solo income statement in any year - only a Consolidated (Group) income statement and comprehensive income statement are published, each year's own Bank Balance Sheet page noting the Bank's own profit-after-tax figure separately (used here to build the Statement of Changes in Equity, which the Bank DOES publish on a solo basis every year). The Balance Sheet and Statement of Changes in Equity sheets in this workbook are therefore Bank/solo basis (consistent with the existing Cash Flow Statement sheet), while the Profit &amp; Loss sheet is necessarily Consolidated (Group) basis - the only income statement this entity discloses. Group and Bank scope differ only immaterially here (a small non-trading subsidiary), so the two bases are not directly comparable line-by-line but both are genuine, source-disclosed figures, not derived or estimated.
 FINANCIAL INVESTMENTS BREAKDOWN: the 'Financial investments - ...' sub-rows below the headline 'Total financial investments' line are transcribed from Note 14 'Financial investments' (Note 14(a) 'Financial Investments by category' and Note 14(b) ECL impairment summary) of each year's own Notes to the Financial Statements, which splits the balance both by measurement basis (amortised cost / fair value through profit or loss (FVTPL) / fair value through other comprehensive income (FVOCI)) and, within the amortised-cost bucket, by issuer type (GCC government bonds/Sukuk and similar instruments; issued by banks and other financial institutions; issued by corporate bodies):
 FY2025/FY2024 (own): Annual Report and Financial Statements 2025, Note 14, p.52 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023 (own) / FY2022 (comparative): Annual Report and Financial Statements 2023, Note 14, p.48 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQxNzM5MjkxNGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023 (own) / FY2022 (comparative): Annual Report and Financial Statements 2023, Note 14, p.48 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQxNzM5MjkxNGFkaXF6a2N4/document?format=pdf&amp;download=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="409" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 FY2022 (own) / FY2021 (comparative): Annual Report and Financial Statements 2022, Note 14, p.47 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2021 (own): Annual Report and Financial Statements 2021, Note 14, p.38 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM0MTg2NjEyNWFkaXF6a2N4/document?format=pdf&amp;download=0
 The three amortised-cost issuer-type sub-rows are gross carrying amounts (Note 14(a)'s own 'Quoted investments' lines); the 'ECL impairment provision' sub-row is that same note's single aggregate impairment allowance (Note 14(b), not broken down by issuer), so the four amortised-cost sub-rows plus the FVTPL and FVOCI sub-rows sum exactly to that year's headline 'Total financial investments' line every year. GCC government bonds and debt securities are labelled 'GCC government Sukuk and similar instruments' from FY2024 onward, reflecting the FY2024 Shariah conversion (see ENTITY_NOTE) - the same amortised-cost sovereign-debt line, kept under each year's own originally-printed wording rather than forced into a single common label.</t>
@@ -4969,8 +4986,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5569,7 +5587,7 @@
         <v>55841</v>
       </c>
     </row>
-    <row r="30" ht="420" customHeight="1">
+    <row r="30" ht="409" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Kuwait Finance House Plc's (formerly Ahli United Bank (UK) PLC's) own Annual Report and Financial Statements, from Companies House filings:
@@ -6316,7 +6334,7 @@
         <v>332609</v>
       </c>
     </row>
-    <row r="41" ht="150" customHeight="1">
+    <row r="41" ht="325" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Kuwait Finance House Plc's (formerly Ahli United Bank (UK) PLC's) own Annual Report and Financial Statements, from Companies House filings:
@@ -7742,7 +7760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="86" customWidth="1" min="1" max="1"/>
@@ -7895,7 +7913,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="460" customHeight="1">
+    <row r="8" ht="409" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>NOT APPLICABLE - Kuwait Finance House Plc does not use the UK KM1 key-metrics template in any year. This is an affirmative finding read off the documents, not the result of a search that failed to find a table.
@@ -7905,14 +7923,22 @@
 THE FIVE RATIOS THEMSELVES ARE ALREADY IN THIS WORKBOOK, on the CET1 Ratio, Total Capital Ratio, Leverage Ratio, LCR and NSFR sheets, each with its own citation. Nothing is lost by this sheet carrying no rows.
 AN EXTRACTION CAVEAT WORTH RECORDING (map rules 13 and 15). Every Companies House filing for this company is a whole-document scan: pdftotext returns 91 characters for the entire 91-page FY2025 filing, and pdfimages confirms one full-page CCITT bitmap per page. Any keyword search over these documents therefore returns zero for everything, and a zero from that instrument says nothing whatever about the bank. The finding above was made by RENDERING the appendix pages at 150dpi and reading them by eye, which is the only instrument that works on this filing set.
 LATEST-EDITION CHECK (required by the KM1 map), performed 2026-09-17. The bank's own web presence, kfhuk.com, is a single-page holding site: its robots.txt points at /sitemap.xml, and that sitemap contains exactly one URL (/lander). There is no investor, results or regulatory-disclosures section to check, and no Pillar 3 document is published on the bank's website at all - which is consistent with, and explains, the disclosure living inside the Companies House filing. The newest filing available is the Annual Report and Financial Statements 2025 (FY2025), which is already this workbook's most recent year. NONE NEWER EXISTS; this workbook is not an edition behind.
-NOTE ON kfh.co.uk, recorded so a later session does not repeat the mistake: that domain is NOT this bank. It belongs to Kinleigh Folkard &amp; Hayward, a London estate agency, and it resolves and serves a normal site - so an automated check that assumed the obvious domain would have read an unrelated company's pages as this bank's.
+NOTE ON kfh.co.uk, recorded so a later session does not repeat the mistake: that domain is NOT this bank. It belongs to Kinleigh Folkard &amp; Hayward, a London estate agency, and it resolves and serves a normal site - so an automated check that assumed the obvious domain would have read an unrelated company's pages as this bank's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="409" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 ENTITY NOTE: Kuwait Finance House Plc (FRN 131818, Companies House 00877859) was formerly Ahli United Bank (UK) PLC - renamed following its 2024 conversion to a Shariah-compliant (Islamic) bank under new ownership (Kuwait Finance House Group), confirmed by the FY2024/FY2025 Annual Reports' own Shariah Supervisory Board report describing 'the recent conversion of the Bank'. This is a genuine, disclosed business-model change, not a data anomaly: FY2021-FY2023 use conventional banking terminology (Loans and advances, Interest income/expense/receivable/payable); FY2024-FY2025 use Islamic-finance terminology (Financing receivables, Returns receivable/payable) for the functionally equivalent line items, kept as each year's own originally-printed labels rather than forced into a single common wording. Reports in USD'000 (Bank/solo basis) - all Companies House filings are fully scanned/image-only, transcribed via targeted page-image reads, not full-document OCR. Kept in native USD (not converted to GBP), consistent with sibling USD-reporting banks built in this same batch (e.g. Itau BBA International plc).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
+++ b/banks/KUWAIT FINANCE HOUSE FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2932,7 +2933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2946,14 +2947,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Tier 1 Capital</t>
+          <t>Kuwait Finance House Plc — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -2992,34 +2993,37 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>325.3</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>316.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>323.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: No Additional Tier 1 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout. A small Tier 2 balance ($799k) exists only in FY2021 (see Total Capital), fully amortised/repaid by FY2022 onward.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="280" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>CET1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>19.9%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="280" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
@@ -3030,9 +3034,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3058,14 +3061,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Tier 1 Ratio</t>
+          <t>Kuwait Finance House Plc — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>USD m</t>
         </is>
       </c>
     </row>
@@ -3104,33 +3107,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>19.9%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>319</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -3166,7 +3159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3180,14 +3173,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Total Capital</t>
+          <t>Kuwait Finance House Plc — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3226,27 +3219,44 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital / Own Funds</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>325.3</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>316.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>323.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>319.8</v>
-      </c>
-    </row>
-    <row r="6" ht="280" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>19.9%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: No Additional Tier 1 instruments disclosed any year - Tier 1 capital equals CET1 capital throughout. A small Tier 2 balance ($799k) exists only in FY2021 (see Total Capital), fully amortised/repaid by FY2022 onward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
 FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
@@ -3257,8 +3267,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3284,14 +3295,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — Total Capital Ratio</t>
+          <t>Kuwait Finance House Plc — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>USD m</t>
         </is>
       </c>
     </row>
@@ -3330,33 +3341,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>19.9%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22.5%</t>
-        </is>
+          <t>Total capital / Own Funds</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>319.8</v>
       </c>
     </row>
     <row r="6" ht="280" customHeight="1">
@@ -3379,6 +3380,120 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>19.9%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>22.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="280" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
+FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3504,7 +3619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3697,7 +3812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3816,120 +3931,6 @@
   <mergeCells count="2">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kuwait Finance House Plc — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Liquidity Coverage Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>592.3%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>385.4%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>662.5%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>392.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>486.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="280" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
-FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3955,7 +3956,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — NSFR</t>
+          <t>Kuwait Finance House Plc — LCR</t>
         </is>
       </c>
     </row>
@@ -4001,32 +4002,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Net Stable Funding Ratio</t>
+          <t>Liquidity Coverage Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>139.0%</t>
+          <t>592.3%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>385.4%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>133.0%</t>
+          <t>662.5%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>392.5%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>136.2%</t>
+          <t>486.4%</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4056,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -4069,12 +4070,16 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — MREL Ratio</t>
+          <t>Kuwait Finance House Plc — NSFR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -4111,47 +4116,40 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>MREL Ratio</t>
+          <t>Net Stable Funding Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable – no MREL above MCR: KFH Plc absent from BoE 'External MRELs' lists 2023–26, which name every UK resolution entity with MREL above MCR; AR FY2025 (incl. Pillar 3) has none.</t>
+          <t>139.0%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable – no MREL above MCR: KFH Plc absent from BoE 'External MRELs' lists 2023–26, which name every UK resolution entity with MREL above MCR; AR FY2024 (incl. Pillar 3) has none.</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not applicable – no MREL above MCR: KFH Plc absent from BoE 'External MRELs' lists 2023–26, which name every UK resolution entity with MREL above MCR; AR FY2023 (incl. Pillar 3) has none.</t>
+          <t>133.0%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not published – no MREL figure in KFH Plc Annual Report FY2022 or its Pillar 3 appendix (CH scan, OCR 2026-09-19).</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not published – no MREL figure in KFH Plc Annual Report FY2021 or its Pillar 3 appendix (CH scan, OCR 2026-09-19).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="91" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed any year. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): this note previously read 'consistent with a small UK bank subsidiary that is not itself a resolution entity' - a plausibility argument rather than evidence. The Bank of England's own 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures - the 2023, 2024, 2025 and 2026 editions at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt; - contain, in the BoE's own words, 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated'. KFH is named in none of the four editions. As a UK subsidiary of Kuwait Finance House K.S.C.P., whose resolution entity is not incorporated in the UK, that absence is exactly what the scope sentence predicts, and the reasoning in this note is now sourced rather than assumed. The BoE publishes the REQUIREMENT, not the ratio, so nothing from that table is transcribed here - it establishes that there was nothing for the Bank to disclose.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="156" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>136.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="280" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
-FY2025/FY2024: p.n/a - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
 Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
@@ -4159,9 +4157,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4989,6 +4986,124 @@
   <mergeCells count="2">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A43:F43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – no MREL above MCR: KFH Plc absent from BoE 'External MRELs' lists 2023–26, which name every UK resolution entity with MREL above MCR; AR FY2025 (incl. Pillar 3) has none.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – no MREL above MCR: KFH Plc absent from BoE 'External MRELs' lists 2023–26, which name every UK resolution entity with MREL above MCR; AR FY2024 (incl. Pillar 3) has none.</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not applicable – no MREL above MCR: KFH Plc absent from BoE 'External MRELs' lists 2023–26, which name every UK resolution entity with MREL above MCR; AR FY2023 (incl. Pillar 3) has none.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in KFH Plc Annual Report FY2022 or its Pillar 3 appendix (CH scan, OCR 2026-09-19).</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no MREL figure in KFH Plc Annual Report FY2021 or its Pillar 3 appendix (CH scan, OCR 2026-09-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="91" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed any year. POSITIVE RECORD ADDED 18 September 2026 (KM1-032): this note previously read 'consistent with a small UK bank subsidiary that is not itself a resolution entity' - a plausibility argument rather than evidence. The Bank of England's own 'External minimum requirements for own funds and eligible liabilities (MRELs)' disclosures - the 2023, 2024, 2025 and 2026 editions at bankofengland.co.uk/financial-stability/resolution/mrels-&lt;year&gt; - contain, in the BoE's own words, 'all firms with a resolution entity incorporated in the UK for which an MREL above MCR has been communicated'. KFH is named in none of the four editions. As a UK subsidiary of Kuwait Finance House K.S.C.P., whose resolution entity is not incorporated in the UK, that absence is exactly what the scope sentence predicts, and the reasoning in this note is now sourced rather than assumed. The BoE publishes the REQUIREMENT, not the ratio, so nothing from that table is transcribed here - it establishes that there was nothing for the Bank to disclose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="156" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
+FY2025/FY2024: p.n/a - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
+Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7760,6 +7875,266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kuwait Finance House Plc — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Not computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Return on average equity (share capital and reserves) (as published)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>6.59%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Return on average total assets (as published)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="325" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Note: TWO KINDS OF FIGURE, NEVER MERGED. The rows above are not one series. The 'Return on equity/assets' rows are THIS PROJECT'S OWN ARITHMETIC on the figures printed on this workbook's statement sheets. The rows marked '(as published)' are the bank's own published ratios, quoted verbatim, each struck on the bank's own definition - which differs from bank to bank and usually from ours, most often in whether the numerator is before or after tax and whether the denominator is average, opening or year-end equity, tangible equity or required equity. They are not averaged, reconciled, or substituted for one another, and where they disagree both stand: the disagreement is the finding.
+THE BANK'S OWN DEFINITIONS, VERBATIM. Return on average equity (share capital and reserves): “The label itself is the only definition the document gives: 'average equity (share capital and reserves)'. No basis-of-calculation note accompanies the table.” Return on average total assets: “The label itself is the only definition the document gives: 'average total assets'. No basis-of-calculation note accompanies the table.”
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return.
+FY2021 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2021 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2021 because it needs only the closing balance.
+WHY EVERY COMPUTED CELL SAYS 'NOT COMPUTED', AND IT IS NOT A CURRENCY PROBLEM. Balance Sheet is Bank/solo; Profit &amp; Loss is Consolidated (Group) - the entity publishes no standalone Bank income statement, which the script states. A ratio divides GROUP profit by SOLO equity/assets. The two statement sheets print the same unit, so a ratio across them cancels its unit perfectly and would pass every check this project runs - and it would still be one entity's profit over another entity's balance sheet, which is not a return on anything. A group figure is a different claim from a solo figure, so the ratio is refused rather than printed with a caveat. The underlying figures are all on this workbook's statement sheets, each labelled with the entity it belongs to, for a reader who wants to strike a ratio on a single perimeter.
+FIGURES THE BANK PUBLISHED ONLY AS A LATER EDITION'S COMPARATIVE, AND WHY THEY ARE NOT IN THE CELLS ABOVE. FY2024 Return on average equity (share capital and reserves) 11.71%; FY2024 Return on average total assets 1.29%. Each year's cell carries what that year's OWN annual report printed. A comparative restated in a later edition is a different claim - it may rest on a revised definition, a restated perimeter or a corrected prior figure - so it is recorded here rather than substituted into the year it refers to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="170" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “net profit after tax” and the Balance Sheet rows “total equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Kuwait Finance House Plc's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The '(as published)' rows are quoted verbatim from Kuwait Finance House Plc's own disclosures and are recorded, with the exact document, page and verification state for each, in research/profitability/published_returns.jsonl under ‘KUWAIT FINANCE HOUSE’.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7939,110 +8314,6 @@
   <mergeCells count="2">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A10:F10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kuwait Finance House Plc — CET1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>USD m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>325.3</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>316.7</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>323.2</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="6" ht="280" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Kuwait Finance House Plc (formerly Ahli United Bank (UK) PLC) Appendix: Pillar 3 Disclosures (unaudited), Key Metrics table, published within each year's own Annual Report and Financial Statements:
-FY2025/FY2024: p.83 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzUyMTMwODAyMGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Annual Report 2024, p.85 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzQ2OTUzMTA5NGFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022/FY2021: Annual Report 2022, p.72 - https://find-and-update.company-information.service.gov.uk/company/00877859/filing-history/MzM3MTE2OTUwOGFkaXF6a2N4/document?format=pdf&amp;download=0
-Total RWAs are NOT separately disclosed anywhere in the source (Note 33/Capital Adequacy explicitly defers to the Pillar 3 appendix, which gives ratios and Own Funds only, no RWA figure), so the Total RWAs sheet reads 'Not publicly disclosed'. A back-solved series (Own Funds / Total Capital ratio) previously stood there and was WITHDRAWN 2026-09-16 - see that sheet's own note for the withdrawal record. What the bank does disclose by risk category is on the RWA Breakdown sheet, derived from the appendix's own published Pillar 1 minimum capital requirements.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8068,14 +8339,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kuwait Finance House Plc — CET1 Ratio</t>
+          <t>Kuwait Finance House Plc — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>USD m</t>
         </is>
       </c>
     </row>
@@ -8114,33 +8385,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>CET1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.4%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>19.9%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>319</v>
       </c>
     </row>
     <row r="6" ht="280" customHeight="1">
